--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/ss_inv/AS_pos_ssinv_mark_vf2.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/ss_inv/AS_pos_ssinv_mark_vf2.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\ss_inv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA9D03B-0F08-49D2-B4A2-CF01FCDBBD2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548A628C-544D-4599-85CB-54A6DE39C3E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
@@ -274,6 +277,41 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Contrainte de capacité"/>
+      <sheetName val="results"/>
+      <sheetName val="Feuil1"/>
+      <sheetName val="Feuil2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="AD3">
+            <v>-544740.82216742123</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AE4">
+            <v>-483581.00663625158</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AF5">
+            <v>-3.716445296378966</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.35">
@@ -1175,6 +1213,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="AD11" s="4">
+        <f>(AD3-[1]results!$AD$3)/[1]results!$AD$3</f>
+        <v>6.397369539733333E-2</v>
+      </c>
+      <c r="AE11" s="4">
+        <f>(AE4-[1]results!$AE$4)/[1]results!$AE$4</f>
+        <v>1.159060261966567E-2</v>
+      </c>
+      <c r="AF11" s="4">
+        <f>(AF5-[1]results!$AF$5)/[1]results!$AF$5</f>
+        <v>7.7322452721611951E-2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
